--- a/site/exports/uestc-medicine.xlsx
+++ b/site/exports/uestc-medicine.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>医学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>本科学位授予明确但授位时间未知。；博士阶段毕业、学位标题不作明确授位，页面内科学（重症）与临床医学博士专业学位标签保留其不同语义。；邱海波为明确博士学习阶段师从，不推正式论文导师或具体指导日期。；官网“专职”等表述只存为来源标签，实时现职未知，导航关闭。；来源记载职业信息：来源职称表述：副研究员。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。；来源记载职业信息：专业方向：重症医学。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,11 +638,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="29.4" customWidth="1" min="2" max="2"/>
+    <col width="43.4" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16.8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1012,14 +1066,224 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2009-06</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>临床医学</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>个人简介明确获得临床医学学士学位，但2004是入学年、2009.06是学习终点；两者均不当授位日期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：医学院</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>combined_masters_doctoral_study</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>内科学（重症）</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>硕博连读攻读博士并顺利毕业，未见明确取得博士学位；不补独立硕士学位或授位日期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：医学院；来源记载（source_profile_degree_label）：临床医学博士专业学位</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>visiting_scholar</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>美国加州大学旧金山分校</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>访问学者是非学位经历；没有导师披露，不从合作者或博士阶段导师补入。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1031,18 +1295,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="18.2" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1110,8 +1374,61 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>邱海波</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentorship</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>硕博连读攻读内科学博士阶段</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；Source-mentioned name only; no independent mentor identity node, biography or present employment. Stage dates are in education event; exact supervision start/end unknown. Not a formal dissertation-advisor assertion.；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1122,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1134,7 +1451,7 @@
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="36.4" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1305,13 +1622,113 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>干细胞治疗急性肺损伤的研究进展</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_source_reported：贺宏丽、邱海波*；来源书目信息（卷）：23；来源书目信息（期）：1；来源书目信息（页码）：52-54</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>急性肺损伤/急性呼吸窘迫综合征基因治疗进展</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_source_reported：贺宏丽、陈秋华、刘玲、邱海波*；来源书目信息（卷）：22；来源书目信息（期）：3；来源书目信息（页码）：229-233</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1323,14 +1740,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="19.6" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1483,12 +1900,88 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-uestc-hehongli-s001-9694cda45ee8</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20543?yxsh=13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:38:42Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>贺宏丽</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-uestc-hehongli-s002-58d7b7bb1a74</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/index/</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:39:01Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/uestc-medicine.xlsx
+++ b/site/exports/uestc-medicine.xlsx
@@ -1107,7 +1107,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L7" s="2" t="b">
@@ -1178,7 +1178,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
